--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>67.71736625923612</v>
+        <v>11.00407201712587</v>
       </c>
       <c r="D2" t="n">
-        <v>67.69808901087455</v>
+        <v>11.00093946426712</v>
       </c>
       <c r="E2" t="n">
-        <v>11.05027439212894</v>
+        <v>1.795669588720953</v>
       </c>
       <c r="F2" t="n">
-        <v>11.04589211522099</v>
+        <v>1.794957468723411</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.75754019365015</v>
+        <v>7.59810028146815</v>
       </c>
       <c r="D3" t="n">
-        <v>46.75916359165084</v>
+        <v>7.598364083643261</v>
       </c>
       <c r="E3" t="n">
-        <v>11.05027439212894</v>
+        <v>1.795669588720953</v>
       </c>
       <c r="F3" t="n">
-        <v>11.04589211522099</v>
+        <v>1.794957468723411</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.22139940028034</v>
+        <v>8.648477402545556</v>
       </c>
       <c r="D4" t="n">
-        <v>53.27964500902782</v>
+        <v>8.65794231396702</v>
       </c>
       <c r="E4" t="n">
-        <v>11.05027439212894</v>
+        <v>1.795669588720953</v>
       </c>
       <c r="F4" t="n">
-        <v>11.04589211522099</v>
+        <v>1.794957468723411</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>49.13018187890331</v>
+        <v>7.983654555321788</v>
       </c>
       <c r="D5" t="n">
-        <v>49.1836864472136</v>
+        <v>7.992349047672211</v>
       </c>
       <c r="E5" t="n">
-        <v>11.05027439212894</v>
+        <v>1.795669588720953</v>
       </c>
       <c r="F5" t="n">
-        <v>11.04589211522099</v>
+        <v>1.794957468723411</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>74.9964296111939</v>
+        <v>12.18691981181901</v>
       </c>
       <c r="D6" t="n">
-        <v>75.04142270137442</v>
+        <v>12.19423118897334</v>
       </c>
       <c r="E6" t="n">
-        <v>11.05027439212894</v>
+        <v>1.795669588720953</v>
       </c>
       <c r="F6" t="n">
-        <v>11.04589211522099</v>
+        <v>1.794957468723411</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
